--- a/data/dividends_info_20260508.xlsx
+++ b/data/dividends_info_20260508.xlsx
@@ -523,10 +523,10 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>47.82500076293945</v>
+        <v>49.03499984741211</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1881860921364434</v>
+        <v>0.1835423682676933</v>
       </c>
       <c r="J2" t="n">
         <v>311</v>
@@ -570,10 +570,10 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>57.09999847412109</v>
+        <v>57.25</v>
       </c>
       <c r="I3" t="n">
-        <v>1.225919472339837</v>
+        <v>1.222707423580786</v>
       </c>
       <c r="J3" t="n">
         <v>290</v>
@@ -617,10 +617,10 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>9.659999847412109</v>
+        <v>9.680000305175781</v>
       </c>
       <c r="I4" t="n">
-        <v>0.621118022233446</v>
+        <v>0.6198346912026306</v>
       </c>
       <c r="J4" t="n">
         <v>220</v>
@@ -711,10 +711,10 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>47.79499816894531</v>
+        <v>49.03499984741211</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1883042231362136</v>
+        <v>0.1835423682676933</v>
       </c>
       <c r="J6" t="n">
         <v>220</v>
@@ -758,10 +758,10 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>2.089999914169312</v>
+        <v>2.065000057220459</v>
       </c>
       <c r="I7" t="n">
-        <v>3.68421067761643</v>
+        <v>3.728813455997861</v>
       </c>
       <c r="J7" t="n">
         <v>199</v>
@@ -805,10 +805,10 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>5.920000076293945</v>
+        <v>5.860000133514404</v>
       </c>
       <c r="I8" t="n">
-        <v>3.378378334839559</v>
+        <v>3.412969205515265</v>
       </c>
       <c r="J8" t="n">
         <v>192</v>
@@ -852,10 +852,10 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>6.099999904632568</v>
+        <v>6.300000190734863</v>
       </c>
       <c r="I9" t="n">
-        <v>0.9836065727547595</v>
+        <v>0.9523809235472627</v>
       </c>
       <c r="J9" t="n">
         <v>164</v>
@@ -946,10 +946,10 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>5</v>
+        <v>5.019999980926514</v>
       </c>
       <c r="I11" t="n">
-        <v>1</v>
+        <v>0.9960159400393419</v>
       </c>
       <c r="J11" t="n">
         <v>150</v>
@@ -993,10 +993,10 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>4.980000019073486</v>
+        <v>4.96999979019165</v>
       </c>
       <c r="I12" t="n">
-        <v>0.7630522059128382</v>
+        <v>0.7645875574279384</v>
       </c>
       <c r="J12" t="n">
         <v>143</v>
@@ -1040,10 +1040,10 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>47.79499816894531</v>
+        <v>49.03499984741211</v>
       </c>
       <c r="I13" t="n">
-        <v>0.1883042231362136</v>
+        <v>0.1835423682676933</v>
       </c>
       <c r="J13" t="n">
         <v>136</v>
@@ -1134,10 +1134,10 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>4.980000019073486</v>
+        <v>4.96999979019165</v>
       </c>
       <c r="I15" t="n">
-        <v>0.7630522059128382</v>
+        <v>0.7645875574279384</v>
       </c>
       <c r="J15" t="n">
         <v>87</v>
@@ -1181,10 +1181,10 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>5.920000076293945</v>
+        <v>6.010000228881836</v>
       </c>
       <c r="I16" t="n">
-        <v>4.222972918549448</v>
+        <v>4.159733618621054</v>
       </c>
       <c r="J16" t="n">
         <v>80</v>
@@ -1228,10 +1228,10 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>9.661999702453613</v>
+        <v>9.625</v>
       </c>
       <c r="I17" t="n">
-        <v>2.690954336647044</v>
+        <v>2.701298701298701</v>
       </c>
       <c r="J17" t="n">
         <v>73</v>
@@ -1275,10 +1275,10 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>15.64000034332275</v>
+        <v>15.30000019073486</v>
       </c>
       <c r="I18" t="n">
-        <v>3.836317051336641</v>
+        <v>3.921568578563408</v>
       </c>
       <c r="J18" t="n">
         <v>73</v>
@@ -1322,10 +1322,10 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>3.720000028610229</v>
+        <v>3.71399998664856</v>
       </c>
       <c r="I19" t="n">
-        <v>5.91397844913971</v>
+        <v>5.923532600723665</v>
       </c>
       <c r="J19" t="n">
         <v>73</v>
@@ -1416,10 +1416,10 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>6.309999942779541</v>
+        <v>6.25</v>
       </c>
       <c r="I21" t="n">
-        <v>1.584786068253912</v>
+        <v>1.6</v>
       </c>
       <c r="J21" t="n">
         <v>73</v>
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>5.570000171661377</v>
+        <v>5.610000133514404</v>
       </c>
       <c r="I23" t="n">
-        <v>2.154398497338059</v>
+        <v>2.139037382247361</v>
       </c>
       <c r="J23" t="n">
         <v>66</v>
@@ -1651,10 +1651,10 @@
         </is>
       </c>
       <c r="H26" t="n">
-        <v>3.940000057220459</v>
+        <v>3.980000019073486</v>
       </c>
       <c r="I26" t="n">
-        <v>1.776649720390682</v>
+        <v>1.75879396142052</v>
       </c>
       <c r="J26" t="n">
         <v>59</v>
@@ -1698,10 +1698,10 @@
         </is>
       </c>
       <c r="H27" t="n">
-        <v>36.59999847412109</v>
+        <v>37.25</v>
       </c>
       <c r="I27" t="n">
-        <v>0.4098360826601156</v>
+        <v>0.4026845637583892</v>
       </c>
       <c r="J27" t="n">
         <v>59</v>
@@ -1745,10 +1745,10 @@
         </is>
       </c>
       <c r="H28" t="n">
-        <v>5.650000095367432</v>
+        <v>5.849999904632568</v>
       </c>
       <c r="I28" t="n">
-        <v>0.7079645898200416</v>
+        <v>0.6837606949074361</v>
       </c>
       <c r="J28" t="n">
         <v>52</v>
@@ -1792,10 +1792,10 @@
         </is>
       </c>
       <c r="H29" t="n">
-        <v>23.36000061035156</v>
+        <v>23.26000022888184</v>
       </c>
       <c r="I29" t="n">
-        <v>1.070205451489659</v>
+        <v>1.074806524247477</v>
       </c>
       <c r="J29" t="n">
         <v>45</v>
@@ -1886,10 +1886,10 @@
         </is>
       </c>
       <c r="H31" t="n">
-        <v>1.870000004768372</v>
+        <v>1.914999961853027</v>
       </c>
       <c r="I31" t="n">
-        <v>1.764705877853063</v>
+        <v>1.723237632238276</v>
       </c>
       <c r="J31" t="n">
         <v>45</v>
@@ -1933,10 +1933,10 @@
         </is>
       </c>
       <c r="H32" t="n">
-        <v>5.085000038146973</v>
+        <v>5.144999980926514</v>
       </c>
       <c r="I32" t="n">
-        <v>5.703048138140802</v>
+        <v>5.6365403513136</v>
       </c>
       <c r="J32" t="n">
         <v>45</v>
@@ -1980,10 +1980,10 @@
         </is>
       </c>
       <c r="H33" t="n">
-        <v>3.898000001907349</v>
+        <v>3.910000085830688</v>
       </c>
       <c r="I33" t="n">
-        <v>4.104669059048478</v>
+        <v>4.09207152142575</v>
       </c>
       <c r="J33" t="n">
         <v>45</v>
@@ -2027,10 +2027,10 @@
         </is>
       </c>
       <c r="H34" t="n">
-        <v>2.611999988555908</v>
+        <v>2.614000082015991</v>
       </c>
       <c r="I34" t="n">
-        <v>5.306278736878078</v>
+        <v>5.302218655368509</v>
       </c>
       <c r="J34" t="n">
         <v>45</v>
@@ -2074,10 +2074,10 @@
         </is>
       </c>
       <c r="H35" t="n">
-        <v>53.84999847412109</v>
+        <v>53.15999984741211</v>
       </c>
       <c r="I35" t="n">
-        <v>1.169916467690824</v>
+        <v>1.185101583537098</v>
       </c>
       <c r="J35" t="n">
         <v>45</v>
@@ -2121,10 +2121,10 @@
         </is>
       </c>
       <c r="H36" t="n">
-        <v>5.389999866485596</v>
+        <v>5.445000171661377</v>
       </c>
       <c r="I36" t="n">
-        <v>2.597402661742239</v>
+        <v>2.571166126470172</v>
       </c>
       <c r="J36" t="n">
         <v>45</v>
@@ -2215,10 +2215,10 @@
         </is>
       </c>
       <c r="H38" t="n">
-        <v>23.77000045776367</v>
+        <v>23.75</v>
       </c>
       <c r="I38" t="n">
-        <v>3.575935984983863</v>
+        <v>3.578947368421052</v>
       </c>
       <c r="J38" t="n">
         <v>45</v>
@@ -2262,10 +2262,10 @@
         </is>
       </c>
       <c r="H39" t="n">
-        <v>47.79499816894531</v>
+        <v>49.03499984741211</v>
       </c>
       <c r="I39" t="n">
-        <v>0.1883042231362136</v>
+        <v>0.1835423682676933</v>
       </c>
       <c r="J39" t="n">
         <v>45</v>
@@ -2309,10 +2309,10 @@
         </is>
       </c>
       <c r="H40" t="n">
-        <v>6.423999786376953</v>
+        <v>6.464000225067139</v>
       </c>
       <c r="I40" t="n">
-        <v>2.822229234572417</v>
+        <v>2.804764753827293</v>
       </c>
       <c r="J40" t="n">
         <v>45</v>
@@ -2356,10 +2356,10 @@
         </is>
       </c>
       <c r="H41" t="n">
-        <v>8.739999771118164</v>
+        <v>8.720000267028809</v>
       </c>
       <c r="I41" t="n">
-        <v>2.974828453190412</v>
+        <v>2.981651284840964</v>
       </c>
       <c r="J41" t="n">
         <v>45</v>
@@ -2403,10 +2403,10 @@
         </is>
       </c>
       <c r="H42" t="n">
-        <v>9.994000434875488</v>
+        <v>10.01500034332275</v>
       </c>
       <c r="I42" t="n">
-        <v>2.771662877193492</v>
+        <v>2.765851128349513</v>
       </c>
       <c r="J42" t="n">
         <v>45</v>
@@ -2450,10 +2450,10 @@
         </is>
       </c>
       <c r="H43" t="n">
-        <v>1.174999952316284</v>
+        <v>1.200000047683716</v>
       </c>
       <c r="I43" t="n">
-        <v>1.148936216838764</v>
+        <v>1.124999955296518</v>
       </c>
       <c r="J43" t="n">
         <v>38</v>
@@ -2497,10 +2497,10 @@
         </is>
       </c>
       <c r="H44" t="n">
-        <v>3.640000104904175</v>
+        <v>3.671999931335449</v>
       </c>
       <c r="I44" t="n">
-        <v>3.021977934885137</v>
+        <v>2.995642757542065</v>
       </c>
       <c r="J44" t="n">
         <v>38</v>
@@ -2591,10 +2591,10 @@
         </is>
       </c>
       <c r="H46" t="n">
-        <v>3.214999914169312</v>
+        <v>3.130000114440918</v>
       </c>
       <c r="I46" t="n">
-        <v>4.976671983561799</v>
+        <v>5.111820899360551</v>
       </c>
       <c r="J46" t="n">
         <v>31</v>
@@ -2685,10 +2685,10 @@
         </is>
       </c>
       <c r="H48" t="n">
-        <v>27.04999923706055</v>
+        <v>27.35000038146973</v>
       </c>
       <c r="I48" t="n">
-        <v>4.103512130526112</v>
+        <v>4.058500857470011</v>
       </c>
       <c r="J48" t="n">
         <v>27</v>
@@ -2732,10 +2732,10 @@
         </is>
       </c>
       <c r="H49" t="n">
-        <v>0.9129999876022339</v>
+        <v>0.8930000066757202</v>
       </c>
       <c r="I49" t="n">
-        <v>3.285870800369614</v>
+        <v>3.359462460888206</v>
       </c>
       <c r="J49" t="n">
         <v>24</v>
@@ -2779,10 +2779,10 @@
         </is>
       </c>
       <c r="H50" t="n">
-        <v>0.5099999904632568</v>
+        <v>0.5049999952316284</v>
       </c>
       <c r="I50" t="n">
-        <v>4.509804005899691</v>
+        <v>4.554455488549181</v>
       </c>
       <c r="J50" t="n">
         <v>24</v>
@@ -2826,10 +2826,10 @@
         </is>
       </c>
       <c r="H51" t="n">
-        <v>19.64999961853027</v>
+        <v>19.70000076293945</v>
       </c>
       <c r="I51" t="n">
-        <v>3.053435173780819</v>
+        <v>3.045685161234854</v>
       </c>
       <c r="J51" t="n">
         <v>24</v>
@@ -2873,10 +2873,10 @@
         </is>
       </c>
       <c r="H52" t="n">
-        <v>9.079999923706055</v>
+        <v>8.979999542236328</v>
       </c>
       <c r="I52" t="n">
-        <v>2.202643190313694</v>
+        <v>2.227171605736999</v>
       </c>
       <c r="J52" t="n">
         <v>24</v>
@@ -2920,10 +2920,10 @@
         </is>
       </c>
       <c r="H53" t="n">
-        <v>2.559999942779541</v>
+        <v>2.565000057220459</v>
       </c>
       <c r="I53" t="n">
-        <v>7.031250157160687</v>
+        <v>7.017543703100556</v>
       </c>
       <c r="J53" t="n">
         <v>17</v>
@@ -2967,10 +2967,10 @@
         </is>
       </c>
       <c r="H54" t="n">
-        <v>8.300000190734863</v>
+        <v>8.350000381469727</v>
       </c>
       <c r="I54" t="n">
-        <v>3.614457748264686</v>
+        <v>3.592814207119778</v>
       </c>
       <c r="J54" t="n">
         <v>17</v>
@@ -3014,10 +3014,10 @@
         </is>
       </c>
       <c r="H55" t="n">
-        <v>13.52999973297119</v>
+        <v>13.55000019073486</v>
       </c>
       <c r="I55" t="n">
-        <v>1.847745786651985</v>
+        <v>1.845018424213333</v>
       </c>
       <c r="J55" t="n">
         <v>17</v>
@@ -3061,10 +3061,10 @@
         </is>
       </c>
       <c r="H56" t="n">
-        <v>3.430000066757202</v>
+        <v>3.410000085830688</v>
       </c>
       <c r="I56" t="n">
-        <v>0.8746355514903141</v>
+        <v>0.8797653737504787</v>
       </c>
       <c r="J56" t="n">
         <v>17</v>
@@ -3108,10 +3108,10 @@
         </is>
       </c>
       <c r="H57" t="n">
-        <v>3.799999952316284</v>
+        <v>3.809999942779541</v>
       </c>
       <c r="I57" t="n">
-        <v>3.947368470585578</v>
+        <v>3.937007933143675</v>
       </c>
       <c r="J57" t="n">
         <v>17</v>
@@ -3155,10 +3155,10 @@
         </is>
       </c>
       <c r="H58" t="n">
-        <v>14.55000019073486</v>
+        <v>14.25</v>
       </c>
       <c r="I58" t="n">
-        <v>3.986254243277137</v>
+        <v>4.070175438596491</v>
       </c>
       <c r="J58" t="n">
         <v>17</v>
@@ -3202,10 +3202,10 @@
         </is>
       </c>
       <c r="H59" t="n">
-        <v>2.341000080108643</v>
+        <v>2.319000005722046</v>
       </c>
       <c r="I59" t="n">
-        <v>4.442545768523575</v>
+        <v>4.484691666381367</v>
       </c>
       <c r="J59" t="n">
         <v>10</v>
@@ -3249,10 +3249,10 @@
         </is>
       </c>
       <c r="H60" t="n">
-        <v>11.03499984741211</v>
+        <v>10.94999980926514</v>
       </c>
       <c r="I60" t="n">
-        <v>2.628001848754078</v>
+        <v>2.648401872615759</v>
       </c>
       <c r="J60" t="n">
         <v>10</v>
@@ -3296,10 +3296,10 @@
         </is>
       </c>
       <c r="H61" t="n">
-        <v>2.089999914169312</v>
+        <v>2.065000057220459</v>
       </c>
       <c r="I61" t="n">
-        <v>3.68421067761643</v>
+        <v>3.728813455997861</v>
       </c>
       <c r="J61" t="n">
         <v>10</v>
@@ -3343,10 +3343,10 @@
         </is>
       </c>
       <c r="H62" t="n">
-        <v>38.86000061035156</v>
+        <v>38.93000030517578</v>
       </c>
       <c r="I62" t="n">
-        <v>4.220277854455656</v>
+        <v>4.212689409565611</v>
       </c>
       <c r="J62" t="n">
         <v>10</v>
@@ -3390,10 +3390,10 @@
         </is>
       </c>
       <c r="H63" t="n">
-        <v>35.29999923706055</v>
+        <v>35.59000015258789</v>
       </c>
       <c r="I63" t="n">
-        <v>5.665722502056749</v>
+        <v>5.619556030978472</v>
       </c>
       <c r="J63" t="n">
         <v>10</v>
@@ -3437,10 +3437,10 @@
         </is>
       </c>
       <c r="H64" t="n">
-        <v>3.747999906539917</v>
+        <v>3.721999883651733</v>
       </c>
       <c r="I64" t="n">
-        <v>2.66808971434362</v>
+        <v>2.686727649810883</v>
       </c>
       <c r="J64" t="n">
         <v>10</v>
@@ -3484,10 +3484,10 @@
         </is>
       </c>
       <c r="H65" t="n">
-        <v>31.10000038146973</v>
+        <v>31.28000068664551</v>
       </c>
       <c r="I65" t="n">
-        <v>0.4773633381961523</v>
+        <v>0.4746163578678648</v>
       </c>
       <c r="J65" t="n">
         <v>10</v>
@@ -3531,10 +3531,10 @@
         </is>
       </c>
       <c r="H66" t="n">
-        <v>22.15999984741211</v>
+        <v>22.54000091552734</v>
       </c>
       <c r="I66" t="n">
-        <v>4.151624577323449</v>
+        <v>4.081632487273906</v>
       </c>
       <c r="J66" t="n">
         <v>10</v>
@@ -3578,10 +3578,10 @@
         </is>
       </c>
       <c r="H67" t="n">
-        <v>10.52000045776367</v>
+        <v>10.59000015258789</v>
       </c>
       <c r="I67" t="n">
-        <v>2.851710902527599</v>
+        <v>2.832861148983918</v>
       </c>
       <c r="J67" t="n">
         <v>10</v>
@@ -3625,10 +3625,10 @@
         </is>
       </c>
       <c r="H68" t="n">
-        <v>85.26000213623047</v>
+        <v>85.12000274658203</v>
       </c>
       <c r="I68" t="n">
-        <v>1.219798233570606</v>
+        <v>1.221804471854016</v>
       </c>
       <c r="J68" t="n">
         <v>10</v>
@@ -3672,10 +3672,10 @@
         </is>
       </c>
       <c r="H69" t="n">
-        <v>47.38999938964844</v>
+        <v>47.84999847412109</v>
       </c>
       <c r="I69" t="n">
-        <v>1.47710489347021</v>
+        <v>1.462904957831051</v>
       </c>
       <c r="J69" t="n">
         <v>10</v>
@@ -3719,10 +3719,10 @@
         </is>
       </c>
       <c r="H70" t="n">
-        <v>57.09999847412109</v>
+        <v>57.25</v>
       </c>
       <c r="I70" t="n">
-        <v>3.852889770210915</v>
+        <v>3.842794759825328</v>
       </c>
       <c r="J70" t="n">
         <v>10</v>
@@ -3766,10 +3766,10 @@
         </is>
       </c>
       <c r="H71" t="n">
-        <v>9.302000045776367</v>
+        <v>9.331999778747559</v>
       </c>
       <c r="I71" t="n">
-        <v>9.245323540828068</v>
+        <v>9.215602447382611</v>
       </c>
       <c r="J71" t="n">
         <v>10</v>
@@ -3813,10 +3813,10 @@
         </is>
       </c>
       <c r="H72" t="n">
-        <v>12.46000003814697</v>
+        <v>12.5019998550415</v>
       </c>
       <c r="I72" t="n">
-        <v>4.494382008712114</v>
+        <v>4.479283366606158</v>
       </c>
       <c r="J72" t="n">
         <v>10</v>
@@ -3907,10 +3907,10 @@
         </is>
       </c>
       <c r="H74" t="n">
-        <v>10</v>
+        <v>9.699999809265137</v>
       </c>
       <c r="I74" t="n">
-        <v>3</v>
+        <v>3.092783565969242</v>
       </c>
       <c r="J74" t="n">
         <v>10</v>
@@ -3954,10 +3954,10 @@
         </is>
       </c>
       <c r="H75" t="n">
-        <v>2.269999980926514</v>
+        <v>2.240000009536743</v>
       </c>
       <c r="I75" t="n">
-        <v>4.757709291077578</v>
+        <v>4.821428550901461</v>
       </c>
       <c r="J75" t="n">
         <v>10</v>
@@ -4001,10 +4001,10 @@
         </is>
       </c>
       <c r="H76" t="n">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="I76" t="n">
-        <v>2.395348837209303</v>
+        <v>2.423529411764706</v>
       </c>
       <c r="J76" t="n">
         <v>10</v>
@@ -4048,10 +4048,10 @@
         </is>
       </c>
       <c r="H77" t="n">
-        <v>15.69999980926514</v>
+        <v>15.6899995803833</v>
       </c>
       <c r="I77" t="n">
-        <v>4.777070121729542</v>
+        <v>4.780114850593755</v>
       </c>
       <c r="J77" t="n">
         <v>10</v>
@@ -4095,10 +4095,10 @@
         </is>
       </c>
       <c r="H78" t="n">
-        <v>14.46000003814697</v>
+        <v>14.22999954223633</v>
       </c>
       <c r="I78" t="n">
-        <v>2.074688791207255</v>
+        <v>2.108222133876845</v>
       </c>
       <c r="J78" t="n">
         <v>10</v>
@@ -4142,10 +4142,10 @@
         </is>
       </c>
       <c r="H79" t="n">
-        <v>55</v>
+        <v>55.20000076293945</v>
       </c>
       <c r="I79" t="n">
-        <v>1.545454545454545</v>
+        <v>1.539855051180866</v>
       </c>
       <c r="J79" t="n">
         <v>10</v>
@@ -4189,10 +4189,10 @@
         </is>
       </c>
       <c r="H80" t="n">
-        <v>35.84000015258789</v>
+        <v>35.45999908447266</v>
       </c>
       <c r="I80" t="n">
-        <v>2.371651775617038</v>
+        <v>2.397067179768205</v>
       </c>
       <c r="J80" t="n">
         <v>10</v>
@@ -4236,10 +4236,10 @@
         </is>
       </c>
       <c r="H81" t="n">
-        <v>64.66000366210938</v>
+        <v>63.20000076293945</v>
       </c>
       <c r="I81" t="n">
-        <v>2.010516434229337</v>
+        <v>2.056962000485167</v>
       </c>
       <c r="J81" t="n">
         <v>10</v>
@@ -4283,10 +4283,10 @@
         </is>
       </c>
       <c r="H82" t="n">
-        <v>8.060000419616699</v>
+        <v>8.079999923706055</v>
       </c>
       <c r="I82" t="n">
-        <v>7.444168346935813</v>
+        <v>7.425742644373663</v>
       </c>
       <c r="J82" t="n">
         <v>10</v>
@@ -4377,10 +4377,10 @@
         </is>
       </c>
       <c r="H84" t="n">
-        <v>5.920000076293945</v>
+        <v>5.860000133514404</v>
       </c>
       <c r="I84" t="n">
-        <v>3.378378334839559</v>
+        <v>3.412969205515265</v>
       </c>
       <c r="J84" t="n">
         <v>10</v>
@@ -4424,10 +4424,10 @@
         </is>
       </c>
       <c r="H85" t="n">
-        <v>22.86000061035156</v>
+        <v>22.89999961853027</v>
       </c>
       <c r="I85" t="n">
-        <v>4.374453076554931</v>
+        <v>4.366812299816886</v>
       </c>
       <c r="J85" t="n">
         <v>10</v>
@@ -4518,10 +4518,10 @@
         </is>
       </c>
       <c r="H87" t="n">
-        <v>22.90999984741211</v>
+        <v>22.77000045776367</v>
       </c>
       <c r="I87" t="n">
-        <v>1.178524669569122</v>
+        <v>1.185770727149637</v>
       </c>
       <c r="J87" t="n">
         <v>10</v>
@@ -4565,10 +4565,10 @@
         </is>
       </c>
       <c r="H88" t="n">
-        <v>8.220000267028809</v>
+        <v>8.239999771118164</v>
       </c>
       <c r="I88" t="n">
-        <v>2.433089945291349</v>
+        <v>2.427184533439133</v>
       </c>
       <c r="J88" t="n">
         <v>10</v>
@@ -4612,10 +4612,10 @@
         </is>
       </c>
       <c r="H89" t="n">
-        <v>9.045000076293945</v>
+        <v>9.029999732971191</v>
       </c>
       <c r="I89" t="n">
-        <v>2.6533996459438</v>
+        <v>2.65780738756491</v>
       </c>
       <c r="J89" t="n">
         <v>10</v>
@@ -4659,10 +4659,10 @@
         </is>
       </c>
       <c r="H90" t="n">
-        <v>21.5</v>
+        <v>21.57999992370605</v>
       </c>
       <c r="I90" t="n">
-        <v>3.674418604651163</v>
+        <v>3.660797047233395</v>
       </c>
       <c r="J90" t="n">
         <v>10</v>
@@ -4706,10 +4706,10 @@
         </is>
       </c>
       <c r="H91" t="n">
-        <v>5.199999809265137</v>
+        <v>5.260000228881836</v>
       </c>
       <c r="I91" t="n">
-        <v>1.788461604061919</v>
+        <v>1.768060759567112</v>
       </c>
       <c r="J91" t="n">
         <v>10</v>
@@ -4753,10 +4753,10 @@
         </is>
       </c>
       <c r="H92" t="n">
-        <v>6.099999904632568</v>
+        <v>6.300000190734863</v>
       </c>
       <c r="I92" t="n">
-        <v>0.9836065727547595</v>
+        <v>0.9523809235472627</v>
       </c>
       <c r="J92" t="n">
         <v>10</v>
@@ -4800,10 +4800,10 @@
         </is>
       </c>
       <c r="H93" t="n">
-        <v>36.13999938964844</v>
+        <v>36.15999984741211</v>
       </c>
       <c r="I93" t="n">
-        <v>0.9684560207830283</v>
+        <v>0.9679203580667292</v>
       </c>
       <c r="J93" t="n">
         <v>10</v>
@@ -4847,10 +4847,10 @@
         </is>
       </c>
       <c r="H94" t="n">
-        <v>7.235000133514404</v>
+        <v>7.215000152587891</v>
       </c>
       <c r="I94" t="n">
-        <v>7.661368206924256</v>
+        <v>7.682605520128543</v>
       </c>
       <c r="J94" t="n">
         <v>10</v>
@@ -4894,10 +4894,10 @@
         </is>
       </c>
       <c r="H95" t="n">
-        <v>2.259999990463257</v>
+        <v>2.289999961853027</v>
       </c>
       <c r="I95" t="n">
-        <v>2.654867267840171</v>
+        <v>2.620087379890132</v>
       </c>
       <c r="J95" t="n">
         <v>10</v>
@@ -4941,10 +4941,10 @@
         </is>
       </c>
       <c r="H96" t="n">
-        <v>12.89999961853027</v>
+        <v>12.85000038146973</v>
       </c>
       <c r="I96" t="n">
-        <v>1.550387642746198</v>
+        <v>1.556420187258585</v>
       </c>
       <c r="J96" t="n">
         <v>10</v>
@@ -4988,10 +4988,10 @@
         </is>
       </c>
       <c r="H97" t="n">
-        <v>7.400000095367432</v>
+        <v>7.284999847412109</v>
       </c>
       <c r="I97" t="n">
-        <v>1.391891873953898</v>
+        <v>1.41386413393803</v>
       </c>
       <c r="J97" t="n">
         <v>10</v>
@@ -5035,10 +5035,10 @@
         </is>
       </c>
       <c r="H98" t="n">
-        <v>5.877999782562256</v>
+        <v>5.813000202178955</v>
       </c>
       <c r="I98" t="n">
-        <v>3.232392089629814</v>
+        <v>3.268535926229283</v>
       </c>
       <c r="J98" t="n">
         <v>10</v>
@@ -5082,10 +5082,10 @@
         </is>
       </c>
       <c r="H99" t="n">
-        <v>10.34000015258789</v>
+        <v>10.375</v>
       </c>
       <c r="I99" t="n">
-        <v>4.177949648210394</v>
+        <v>4.163855421686747</v>
       </c>
       <c r="J99" t="n">
         <v>10</v>
@@ -5129,10 +5129,10 @@
         </is>
       </c>
       <c r="H100" t="n">
-        <v>27.5</v>
+        <v>27</v>
       </c>
       <c r="I100" t="n">
-        <v>1.6</v>
+        <v>1.62962962962963</v>
       </c>
       <c r="J100" t="n">
         <v>10</v>
@@ -5176,10 +5176,10 @@
         </is>
       </c>
       <c r="H101" t="n">
-        <v>1.049999952316284</v>
+        <v>1.019999980926514</v>
       </c>
       <c r="I101" t="n">
-        <v>2.857142986894471</v>
+        <v>2.941176525586755</v>
       </c>
       <c r="J101" t="n">
         <v>10</v>
@@ -5223,10 +5223,10 @@
         </is>
       </c>
       <c r="H102" t="n">
-        <v>8.460000038146973</v>
+        <v>8.539999961853027</v>
       </c>
       <c r="I102" t="n">
-        <v>5.555555530505009</v>
+        <v>5.503512905145475</v>
       </c>
       <c r="J102" t="n">
         <v>10</v>
@@ -5270,10 +5270,10 @@
         </is>
       </c>
       <c r="H103" t="n">
-        <v>54.56000137329102</v>
+        <v>54.5</v>
       </c>
       <c r="I103" t="n">
-        <v>2.565982340105563</v>
+        <v>2.568807339449541</v>
       </c>
       <c r="J103" t="n">
         <v>10</v>
@@ -5317,10 +5317,10 @@
         </is>
       </c>
       <c r="H104" t="n">
-        <v>4.188000202178955</v>
+        <v>4.163000106811523</v>
       </c>
       <c r="I104" t="n">
-        <v>7.163323436419951</v>
+        <v>7.206341395695339</v>
       </c>
       <c r="J104" t="n">
         <v>10</v>
@@ -5364,10 +5364,10 @@
         </is>
       </c>
       <c r="H105" t="n">
-        <v>13.10000038146973</v>
+        <v>13.14999961853027</v>
       </c>
       <c r="I105" t="n">
-        <v>0.9160305076764956</v>
+        <v>0.9125475549892977</v>
       </c>
       <c r="J105" t="n">
         <v>10</v>
@@ -5411,10 +5411,10 @@
         </is>
       </c>
       <c r="H106" t="n">
-        <v>3.440000057220459</v>
+        <v>3.480000019073486</v>
       </c>
       <c r="I106" t="n">
-        <v>4.941860382914093</v>
+        <v>4.885057444489921</v>
       </c>
       <c r="J106" t="n">
         <v>10</v>
@@ -5458,10 +5458,10 @@
         </is>
       </c>
       <c r="H107" t="n">
-        <v>21.5</v>
+        <v>21.20000076293945</v>
       </c>
       <c r="I107" t="n">
-        <v>3.255813953488372</v>
+        <v>3.30188667362549</v>
       </c>
       <c r="J107" t="n">
         <v>10</v>
@@ -5505,10 +5505,10 @@
         </is>
       </c>
       <c r="H108" t="n">
-        <v>2.420000076293945</v>
+        <v>2.440000057220459</v>
       </c>
       <c r="I108" t="n">
-        <v>1.446280946139471</v>
+        <v>1.434426195869457</v>
       </c>
       <c r="J108" t="n">
         <v>10</v>
@@ -5552,10 +5552,10 @@
         </is>
       </c>
       <c r="H109" t="n">
-        <v>6.110000133514404</v>
+        <v>6.099999904632568</v>
       </c>
       <c r="I109" t="n">
-        <v>5.400981878705585</v>
+        <v>5.409836150151177</v>
       </c>
       <c r="J109" t="n">
         <v>10</v>
@@ -5599,10 +5599,10 @@
         </is>
       </c>
       <c r="H110" t="n">
-        <v>0.9750000238418579</v>
+        <v>0.9729999899864197</v>
       </c>
       <c r="I110" t="n">
-        <v>7.179487003925837</v>
+        <v>7.194244678355753</v>
       </c>
       <c r="J110" t="n">
         <v>10</v>
@@ -5646,10 +5646,10 @@
         </is>
       </c>
       <c r="H111" t="n">
-        <v>49.88000106811523</v>
+        <v>50</v>
       </c>
       <c r="I111" t="n">
-        <v>1.423416168396702</v>
+        <v>1.42</v>
       </c>
       <c r="J111" t="n">
         <v>10</v>
@@ -5693,10 +5693,10 @@
         </is>
       </c>
       <c r="H112" t="n">
-        <v>99</v>
+        <v>97.94999694824219</v>
       </c>
       <c r="I112" t="n">
-        <v>1.363636363636364</v>
+        <v>1.378254254273591</v>
       </c>
       <c r="J112" t="n">
         <v>10</v>
@@ -5740,10 +5740,10 @@
         </is>
       </c>
       <c r="H113" t="n">
-        <v>7.019999980926514</v>
+        <v>7.159999847412109</v>
       </c>
       <c r="I113" t="n">
-        <v>1.13960114269746</v>
+        <v>1.11731845956554</v>
       </c>
       <c r="J113" t="n">
         <v>10</v>
@@ -5834,10 +5834,10 @@
         </is>
       </c>
       <c r="H115" t="n">
-        <v>4.341000080108643</v>
+        <v>4.303999900817871</v>
       </c>
       <c r="I115" t="n">
-        <v>3.91614828064563</v>
+        <v>3.949814217414263</v>
       </c>
       <c r="J115" t="n">
         <v>10</v>
@@ -5928,10 +5928,10 @@
         </is>
       </c>
       <c r="H117" t="n">
-        <v>57.09999847412109</v>
+        <v>56.59999847412109</v>
       </c>
       <c r="I117" t="n">
-        <v>0.7880910893613235</v>
+        <v>0.7950530249673965</v>
       </c>
       <c r="J117" t="n">
         <v>10</v>
@@ -5975,10 +5975,10 @@
         </is>
       </c>
       <c r="H118" t="n">
-        <v>5</v>
+        <v>4.989999771118164</v>
       </c>
       <c r="I118" t="n">
-        <v>0.8</v>
+        <v>0.8016032431808462</v>
       </c>
       <c r="J118" t="n">
         <v>10</v>
@@ -6022,10 +6022,10 @@
         </is>
       </c>
       <c r="H119" t="n">
-        <v>34.59999847412109</v>
+        <v>34.56000137329102</v>
       </c>
       <c r="I119" t="n">
-        <v>3.034682214755999</v>
+        <v>3.038194323717449</v>
       </c>
       <c r="J119" t="n">
         <v>10</v>
@@ -6116,10 +6116,10 @@
         </is>
       </c>
       <c r="H121" t="n">
-        <v>21.21999931335449</v>
+        <v>21.45999908447266</v>
       </c>
       <c r="I121" t="n">
-        <v>1.790763488671994</v>
+        <v>1.770736329038096</v>
       </c>
       <c r="J121" t="n">
         <v>10</v>
@@ -6163,10 +6163,10 @@
         </is>
       </c>
       <c r="H122" t="n">
-        <v>25.14999961853027</v>
+        <v>25.44000053405762</v>
       </c>
       <c r="I122" t="n">
-        <v>2.385685920877414</v>
+        <v>2.358490516526343</v>
       </c>
       <c r="J122" t="n">
         <v>10</v>
@@ -6210,10 +6210,10 @@
         </is>
       </c>
       <c r="H123" t="n">
-        <v>34.15000152587891</v>
+        <v>34</v>
       </c>
       <c r="I123" t="n">
-        <v>1.02489014454295</v>
+        <v>1.029411764705882</v>
       </c>
       <c r="J123" t="n">
         <v>10</v>
@@ -6257,10 +6257,10 @@
         </is>
       </c>
       <c r="H124" t="n">
-        <v>3.599999904632568</v>
+        <v>3.619999885559082</v>
       </c>
       <c r="I124" t="n">
-        <v>0.4722222347318393</v>
+        <v>0.4696132745146338</v>
       </c>
       <c r="J124" t="n">
         <v>10</v>
@@ -6304,10 +6304,10 @@
         </is>
       </c>
       <c r="H125" t="n">
-        <v>2.859999895095825</v>
+        <v>2.819999933242798</v>
       </c>
       <c r="I125" t="n">
-        <v>0.3496503624754485</v>
+        <v>0.3546099374726125</v>
       </c>
       <c r="J125" t="n">
         <v>10</v>
@@ -6398,10 +6398,10 @@
         </is>
       </c>
       <c r="H127" t="n">
-        <v>1.570000052452087</v>
+        <v>1.610000014305115</v>
       </c>
       <c r="I127" t="n">
-        <v>6.369426538796359</v>
+        <v>6.211180069036247</v>
       </c>
       <c r="J127" t="n">
         <v>10</v>
@@ -6445,10 +6445,10 @@
         </is>
       </c>
       <c r="H128" t="n">
-        <v>8.699999809265137</v>
+        <v>8.760000228881836</v>
       </c>
       <c r="I128" t="n">
-        <v>2.988505812645086</v>
+        <v>2.968036452131321</v>
       </c>
       <c r="J128" t="n">
         <v>10</v>
@@ -6492,10 +6492,10 @@
         </is>
       </c>
       <c r="H129" t="n">
-        <v>2.098000049591064</v>
+        <v>2.099999904632568</v>
       </c>
       <c r="I129" t="n">
-        <v>4.399427922701471</v>
+        <v>4.395238294839327</v>
       </c>
       <c r="J129" t="n">
         <v>10</v>
@@ -6539,10 +6539,10 @@
         </is>
       </c>
       <c r="H130" t="n">
-        <v>9.460000038146973</v>
+        <v>9.340000152587891</v>
       </c>
       <c r="I130" t="n">
-        <v>3.699788568590303</v>
+        <v>3.747323279250947</v>
       </c>
       <c r="J130" t="n">
         <v>3</v>
@@ -6727,10 +6727,10 @@
         </is>
       </c>
       <c r="H134" t="n">
-        <v>9.659999847412109</v>
+        <v>9.680000305175781</v>
       </c>
       <c r="I134" t="n">
-        <v>0.621118022233446</v>
+        <v>0.6198346912026306</v>
       </c>
       <c r="J134" t="n">
         <v>3</v>
@@ -6774,10 +6774,10 @@
         </is>
       </c>
       <c r="H135" t="n">
-        <v>19.76000022888184</v>
+        <v>19.95999908447266</v>
       </c>
       <c r="I135" t="n">
-        <v>2.5303643431602</v>
+        <v>2.505010134940144</v>
       </c>
       <c r="J135" t="n">
         <v>3</v>
@@ -6821,10 +6821,10 @@
         </is>
       </c>
       <c r="H136" t="n">
-        <v>2.339999914169312</v>
+        <v>2.259999990463257</v>
       </c>
       <c r="I136" t="n">
-        <v>2.564102658153289</v>
+        <v>2.654867267840171</v>
       </c>
       <c r="J136" t="n">
         <v>3</v>
@@ -6868,10 +6868,10 @@
         </is>
       </c>
       <c r="H137" t="n">
-        <v>16.79999923706055</v>
+        <v>16.65999984741211</v>
       </c>
       <c r="I137" t="n">
-        <v>2.976190611348407</v>
+        <v>3.001200507679883</v>
       </c>
       <c r="J137" t="n">
         <v>3</v>
@@ -6915,10 +6915,10 @@
         </is>
       </c>
       <c r="H138" t="n">
-        <v>4.300000190734863</v>
+        <v>4.28000020980835</v>
       </c>
       <c r="I138" t="n">
-        <v>2.325581292193156</v>
+        <v>2.336448483596635</v>
       </c>
       <c r="J138" t="n">
         <v>3</v>
@@ -7056,10 +7056,10 @@
         </is>
       </c>
       <c r="H141" t="n">
-        <v>4.880000114440918</v>
+        <v>4.949999809265137</v>
       </c>
       <c r="I141" t="n">
-        <v>1.946721265822835</v>
+        <v>1.919191993142792</v>
       </c>
       <c r="J141" t="n">
         <v>3</v>
@@ -7150,10 +7150,10 @@
         </is>
       </c>
       <c r="H143" t="n">
-        <v>7.75</v>
+        <v>7.849999904632568</v>
       </c>
       <c r="I143" t="n">
-        <v>1.161290322580645</v>
+        <v>1.14649682921509</v>
       </c>
       <c r="J143" t="n">
         <v>3</v>
@@ -7244,10 +7244,10 @@
         </is>
       </c>
       <c r="H145" t="n">
-        <v>7.389999866485596</v>
+        <v>7.519999980926514</v>
       </c>
       <c r="I145" t="n">
-        <v>2.976995994245176</v>
+        <v>2.925531922313842</v>
       </c>
       <c r="J145" t="n">
         <v>3</v>
@@ -7291,10 +7291,10 @@
         </is>
       </c>
       <c r="H146" t="n">
-        <v>26.45000076293945</v>
+        <v>25.89999961853027</v>
       </c>
       <c r="I146" t="n">
-        <v>2.306238118732701</v>
+        <v>2.355212389901244</v>
       </c>
       <c r="J146" t="n">
         <v>-4</v>
@@ -7338,10 +7338,10 @@
         </is>
       </c>
       <c r="H147" t="n">
-        <v>3.079999923706055</v>
+        <v>3.049999952316284</v>
       </c>
       <c r="I147" t="n">
-        <v>4.870129990766698</v>
+        <v>4.918032863773797</v>
       </c>
       <c r="J147" t="n">
         <v>-4</v>
@@ -7385,10 +7385,10 @@
         </is>
       </c>
       <c r="H148" t="n">
-        <v>11.5</v>
+        <v>11.39999961853027</v>
       </c>
       <c r="I148" t="n">
-        <v>6.08695652173913</v>
+        <v>6.140351082662987</v>
       </c>
       <c r="J148" t="n">
         <v>-4</v>
@@ -7432,10 +7432,10 @@
         </is>
       </c>
       <c r="H149" t="n">
-        <v>8.75</v>
+        <v>8.579999923706055</v>
       </c>
       <c r="I149" t="n">
-        <v>5.834285714285715</v>
+        <v>5.949883502790219</v>
       </c>
       <c r="J149" t="n">
         <v>-4</v>
@@ -7479,10 +7479,10 @@
         </is>
       </c>
       <c r="H150" t="n">
-        <v>9.024999618530273</v>
+        <v>9.125</v>
       </c>
       <c r="I150" t="n">
-        <v>2.991689877145609</v>
+        <v>2.958904109589041</v>
       </c>
       <c r="J150" t="n">
         <v>-4</v>
@@ -7526,10 +7526,10 @@
         </is>
       </c>
       <c r="H151" t="n">
-        <v>5.954999923706055</v>
+        <v>6.295000076293945</v>
       </c>
       <c r="I151" t="n">
-        <v>5.877414013167272</v>
+        <v>5.559968161367449</v>
       </c>
       <c r="J151" t="n">
         <v>-4</v>
@@ -7620,10 +7620,10 @@
         </is>
       </c>
       <c r="H153" t="n">
-        <v>18</v>
+        <v>17.75</v>
       </c>
       <c r="I153" t="n">
-        <v>4.166666666666666</v>
+        <v>4.225352112676056</v>
       </c>
       <c r="J153" t="n">
         <v>-4</v>
@@ -7667,10 +7667,10 @@
         </is>
       </c>
       <c r="H154" t="n">
-        <v>11.55000019073486</v>
+        <v>11.69999980926514</v>
       </c>
       <c r="I154" t="n">
-        <v>3.722943661463623</v>
+        <v>3.675213735127469</v>
       </c>
       <c r="J154" t="n">
         <v>-4</v>
@@ -7714,10 +7714,10 @@
         </is>
       </c>
       <c r="H155" t="n">
-        <v>4.190000057220459</v>
+        <v>4.21999979019165</v>
       </c>
       <c r="I155" t="n">
-        <v>3.57995221841372</v>
+        <v>3.554502546389648</v>
       </c>
       <c r="J155" t="n">
         <v>-4</v>
@@ -7761,10 +7761,10 @@
         </is>
       </c>
       <c r="H156" t="n">
-        <v>12.46000003814697</v>
+        <v>12.18000030517578</v>
       </c>
       <c r="I156" t="n">
-        <v>1.582415725492426</v>
+        <v>1.618793062888634</v>
       </c>
       <c r="J156" t="n">
         <v>-4</v>
@@ -7808,10 +7808,10 @@
         </is>
       </c>
       <c r="H157" t="n">
-        <v>28.79999923706055</v>
+        <v>28.54999923706055</v>
       </c>
       <c r="I157" t="n">
-        <v>3.819444545625172</v>
+        <v>3.852889770210915</v>
       </c>
       <c r="J157" t="n">
         <v>-4</v>
@@ -7855,10 +7855,10 @@
         </is>
       </c>
       <c r="H158" t="n">
-        <v>59.20000076293945</v>
+        <v>60.5</v>
       </c>
       <c r="I158" t="n">
-        <v>0.7939189086872963</v>
+        <v>0.7768595041322314</v>
       </c>
       <c r="J158" t="n">
         <v>-4</v>
@@ -7902,10 +7902,10 @@
         </is>
       </c>
       <c r="H159" t="n">
-        <v>78.09999847412109</v>
+        <v>77.59999847412109</v>
       </c>
       <c r="I159" t="n">
-        <v>1.536491707355958</v>
+        <v>1.546391782984621</v>
       </c>
       <c r="J159" t="n">
         <v>-4</v>
@@ -7949,10 +7949,10 @@
         </is>
       </c>
       <c r="H160" t="n">
-        <v>25.54999923706055</v>
+        <v>25.60000038146973</v>
       </c>
       <c r="I160" t="n">
-        <v>1.056751499265652</v>
+        <v>1.054687484283932</v>
       </c>
       <c r="J160" t="n">
         <v>-4</v>
@@ -7996,10 +7996,10 @@
         </is>
       </c>
       <c r="H161" t="n">
-        <v>10.35000038146973</v>
+        <v>10.5</v>
       </c>
       <c r="I161" t="n">
-        <v>3.671497449220761</v>
+        <v>3.619047619047619</v>
       </c>
       <c r="J161" t="n">
         <v>-4</v>
@@ -8043,10 +8043,10 @@
         </is>
       </c>
       <c r="H162" t="n">
-        <v>29.29999923706055</v>
+        <v>30</v>
       </c>
       <c r="I162" t="n">
-        <v>1.023890811643914</v>
+        <v>1</v>
       </c>
       <c r="J162" t="n">
         <v>-4</v>
@@ -8090,10 +8090,10 @@
         </is>
       </c>
       <c r="H163" t="n">
-        <v>0.1791999936103821</v>
+        <v>0.1793999969959259</v>
       </c>
       <c r="I163" t="n">
-        <v>3.906250139282622</v>
+        <v>3.901895271580728</v>
       </c>
       <c r="J163" t="n">
         <v>-11</v>
@@ -8137,10 +8137,10 @@
         </is>
       </c>
       <c r="H164" t="n">
-        <v>7.019999980926514</v>
+        <v>7.050000190734863</v>
       </c>
       <c r="I164" t="n">
-        <v>2.279202285394919</v>
+        <v>2.269503484698804</v>
       </c>
       <c r="J164" t="n">
         <v>-11</v>
@@ -8184,10 +8184,10 @@
         </is>
       </c>
       <c r="H165" t="n">
-        <v>2.180000066757202</v>
+        <v>2.115000009536743</v>
       </c>
       <c r="I165" t="n">
-        <v>2.981651284840964</v>
+        <v>3.073286038151707</v>
       </c>
       <c r="J165" t="n">
         <v>-11</v>
@@ -8231,10 +8231,10 @@
         </is>
       </c>
       <c r="H166" t="n">
-        <v>7.570000171661377</v>
+        <v>7.619999885559082</v>
       </c>
       <c r="I166" t="n">
-        <v>3.30250983264024</v>
+        <v>3.280839944286396</v>
       </c>
       <c r="J166" t="n">
         <v>-11</v>
@@ -8278,10 +8278,10 @@
         </is>
       </c>
       <c r="H167" t="n">
-        <v>1.299999952316284</v>
+        <v>1.320000052452087</v>
       </c>
       <c r="I167" t="n">
-        <v>5.384615582121908</v>
+        <v>5.30303009230682</v>
       </c>
       <c r="J167" t="n">
         <v>-11</v>
@@ -8325,10 +8325,10 @@
         </is>
       </c>
       <c r="H168" t="n">
-        <v>7.25</v>
+        <v>7.349999904632568</v>
       </c>
       <c r="I168" t="n">
-        <v>6.896551724137931</v>
+        <v>6.802721176701774</v>
       </c>
       <c r="J168" t="n">
         <v>-18</v>
@@ -8372,10 +8372,10 @@
         </is>
       </c>
       <c r="H169" t="n">
-        <v>19.1299991607666</v>
+        <v>19.29999923706055</v>
       </c>
       <c r="I169" t="n">
-        <v>3.39780464461846</v>
+        <v>3.367875780802348</v>
       </c>
       <c r="J169" t="n">
         <v>-18</v>
@@ -8419,10 +8419,10 @@
         </is>
       </c>
       <c r="H170" t="n">
-        <v>12.71500015258789</v>
+        <v>12.86999988555908</v>
       </c>
       <c r="I170" t="n">
-        <v>4.246952367437397</v>
+        <v>4.195804233113574</v>
       </c>
       <c r="J170" t="n">
         <v>-18</v>
@@ -8466,10 +8466,10 @@
         </is>
       </c>
       <c r="H171" t="n">
-        <v>5.519999980926514</v>
+        <v>5.619999885559082</v>
       </c>
       <c r="I171" t="n">
-        <v>1.811594209158228</v>
+        <v>1.779359466838351</v>
       </c>
       <c r="J171" t="n">
         <v>-18</v>
@@ -8513,10 +8513,10 @@
         </is>
       </c>
       <c r="H172" t="n">
-        <v>8.239999771118164</v>
+        <v>8.060000419616699</v>
       </c>
       <c r="I172" t="n">
-        <v>1.941747626751306</v>
+        <v>1.985111559182883</v>
       </c>
       <c r="J172" t="n">
         <v>-18</v>
@@ -8560,10 +8560,10 @@
         </is>
       </c>
       <c r="H173" t="n">
-        <v>290.2000122070312</v>
+        <v>289.5</v>
       </c>
       <c r="I173" t="n">
-        <v>1.245692573376264</v>
+        <v>1.248704663212435</v>
       </c>
       <c r="J173" t="n">
         <v>-18</v>
@@ -8607,10 +8607,10 @@
         </is>
       </c>
       <c r="H174" t="n">
-        <v>28.5</v>
+        <v>28.79999923706055</v>
       </c>
       <c r="I174" t="n">
-        <v>4.771929824561403</v>
+        <v>4.722222347318394</v>
       </c>
       <c r="J174" t="n">
         <v>-18</v>
@@ -8701,10 +8701,10 @@
         </is>
       </c>
       <c r="H176" t="n">
-        <v>15.59500026702881</v>
+        <v>15.59000015258789</v>
       </c>
       <c r="I176" t="n">
-        <v>3.751202244201406</v>
+        <v>3.752405351342424</v>
       </c>
       <c r="J176" t="n">
         <v>-18</v>
@@ -8748,10 +8748,10 @@
         </is>
       </c>
       <c r="H177" t="n">
-        <v>20.31999969482422</v>
+        <v>20.35000038146973</v>
       </c>
       <c r="I177" t="n">
-        <v>3.100393747350644</v>
+        <v>3.095823037790527</v>
       </c>
       <c r="J177" t="n">
         <v>-18</v>
@@ -8795,10 +8795,10 @@
         </is>
       </c>
       <c r="H178" t="n">
-        <v>145.1999969482422</v>
+        <v>152.0500030517578</v>
       </c>
       <c r="I178" t="n">
-        <v>0.6198347237712497</v>
+        <v>0.5919105438581544</v>
       </c>
       <c r="J178" t="n">
         <v>-18</v>
@@ -8842,10 +8842,10 @@
         </is>
       </c>
       <c r="H179" t="n">
-        <v>70.45999908447266</v>
+        <v>70.5</v>
       </c>
       <c r="I179" t="n">
-        <v>2.442236761792997</v>
+        <v>2.440851063829788</v>
       </c>
       <c r="J179" t="n">
         <v>-18</v>
@@ -8889,10 +8889,10 @@
         </is>
       </c>
       <c r="H180" t="n">
-        <v>26.70000076293945</v>
+        <v>26.20000076293945</v>
       </c>
       <c r="I180" t="n">
-        <v>0.5243445543055001</v>
+        <v>0.5343511294779558</v>
       </c>
       <c r="J180" t="n">
         <v>-25</v>
@@ -9832,7 +9832,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Pattern S.p.A.</t>
+          <t>RAI WAY S.p.A.</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -9849,7 +9849,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>ITALMOBILIARE S.p.A.</t>
+          <t>MFE-MEDIAFOREUROPE N.V.</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -9866,7 +9866,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>MFE-MEDIAFOREUROPE N.V.</t>
+          <t>NEWPRINCES</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -9876,7 +9876,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
@@ -9893,14 +9893,14 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>NEWPRINCES</t>
+          <t>Neodecortech S.p.A.</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -9917,7 +9917,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Neodecortech S.p.A.</t>
+          <t>POLIGRAFICI PRINTING S.p.A.</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -9934,7 +9934,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>POLIGRAFICI PRINTING S.p.A.</t>
+          <t>Pattern S.p.A.</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -9961,7 +9961,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
@@ -9985,7 +9985,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>RCS MediaGroup S.p.A.</t>
+          <t>RECORDATI S.p.A.</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -10002,7 +10002,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>RECORDATI S.p.A.</t>
+          <t>Snam S.p.A.</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -10087,7 +10087,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>INWIT S.p.A.</t>
+          <t>ITALMOBILIARE S.p.A.</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -10097,14 +10097,14 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>RAI WAY S.p.A.</t>
+          <t>RCS MediaGroup S.p.A.</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -10114,14 +10114,14 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>IMMSI S.p.A.</t>
+          <t>INWIT S.p.A.</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -10131,14 +10131,14 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Snam S.p.A.</t>
+          <t>CENTRALE DEL LATTE D'ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -10155,7 +10155,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>GEOX S.p.A.</t>
+          <t>HERA S.p.A.</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -10165,14 +10165,14 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
+          <t>IMMSI S.p.A.</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -10199,14 +10199,14 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Acinque S.p.A.</t>
+          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -10216,7 +10216,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
@@ -10291,7 +10291,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>CENTRALE DEL LATTE D'ITALIA S.p.A.</t>
+          <t>DIGITAL BROS S.p.A.</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -10308,7 +10308,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>HERA S.p.A.</t>
+          <t>Acinque S.p.A.</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -10325,7 +10325,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Digital Value S.p.A.</t>
+          <t>ESPE S.p.A.</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -10335,14 +10335,14 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>ESPE S.p.A.</t>
+          <t>Esprinet S.p.A.</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -10352,7 +10352,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
@@ -10369,14 +10369,14 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Esprinet S.p.A.</t>
+          <t>Fiera Milano S.p.A</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -10403,14 +10403,14 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Fiera Milano S.p.A</t>
+          <t>GEOX S.p.A.</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -10427,7 +10427,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>GEOX S.p.A.</t>
+          <t>Digital Value S.p.A.</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -10437,14 +10437,14 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>DIGITAL BROS S.p.A.</t>
+          <t>GEOX S.p.A.</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -10454,14 +10454,14 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>SABAF S.p.A.</t>
+          <t>SOL S.p.A.</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -10471,14 +10471,14 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>SABAF S.p.A.</t>
+          <t>MOLTIPLY GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -10495,7 +10495,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>REVO Insurance S.p.A.</t>
+          <t>Neodecortech S.p.A.</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -10505,14 +10505,14 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>PROMOTICA S.p.A.</t>
+          <t>OSAI Automation System S.p.A.</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -10522,7 +10522,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
@@ -10546,7 +10546,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>ITALIAN EXHIBITION GROUP S.p.A.</t>
+          <t>PROMOTICA S.p.A.</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -10556,14 +10556,14 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Gabetti Property Solutions S.p.A.</t>
+          <t>SABAF S.p.A.</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -10573,14 +10573,14 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>SALVATORE FERRAGAMO S.p.A.</t>
+          <t>SABAF S.p.A.</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -10597,7 +10597,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Industrie Chimiche Forestali S.p.A.</t>
+          <t>SALVATORE FERRAGAMO S.p.A.</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -10614,7 +10614,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>MOLTIPLY GROUP S.p.A.</t>
+          <t>SALVATORE FERRAGAMO S.p.A.</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -10624,14 +10624,14 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Neodecortech S.p.A.</t>
+          <t>Industrie Chimiche Forestali S.p.A.</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -10641,14 +10641,14 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>GVS S.p.A.</t>
+          <t>REVO Insurance S.p.A.</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -10665,7 +10665,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>SALVATORE FERRAGAMO S.p.A.</t>
+          <t>ITALIAN EXHIBITION GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -10675,14 +10675,14 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>TREVI - Finanziaria Industriale S.p.A.</t>
+          <t>Tinexta S.p.A.</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -10692,14 +10692,14 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>SYS-DAT S.p.A.</t>
+          <t>GVS S.p.A.</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -10716,7 +10716,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Sanlorenzo S.p.A.</t>
+          <t>GEFRAN S.p.A.</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -10726,7 +10726,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
@@ -10743,14 +10743,14 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>TXT E-SOLUTIONS S.p.A.</t>
+          <t>TREVI - Finanziaria Industriale S.p.A.</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -10760,14 +10760,14 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Technoprobe S.p.A.</t>
+          <t>TXT E-SOLUTIONS S.p.A.</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -10784,7 +10784,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Tinexta S.p.A.</t>
+          <t>Technoprobe S.p.A.</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -10801,7 +10801,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>OSAI Automation System S.p.A.</t>
+          <t>Tinexta S.p.A.</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -10811,7 +10811,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
@@ -10886,7 +10886,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>First Capital S.p.A.</t>
+          <t>SYS-DAT S.p.A.</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -10903,7 +10903,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>SOL S.p.A.</t>
+          <t>Gabetti Property Solutions S.p.A.</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -10913,14 +10913,14 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Tinexta S.p.A.</t>
+          <t>Sanlorenzo S.p.A.</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -10937,7 +10937,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>GEFRAN S.p.A.</t>
+          <t>BIESSE S.p.A.</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -10954,7 +10954,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>FINCANTIERI S.p.A.</t>
+          <t>GAROFALO HEALTH CARE S.p.A.</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -10964,14 +10964,14 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Ferretti S.p.A.</t>
+          <t>CAIRO COMMUNICATION S.p.A.</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -10981,14 +10981,14 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>EUROTECH S.p.A.</t>
+          <t>CAREL INDUSTRIES S.p.A.</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -11005,7 +11005,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>ESAUTOMOTION S.p.A.</t>
+          <t>CEMBRE S.p.A.</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -11022,7 +11022,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>EQUITA GROUP S.p.A.</t>
+          <t>CIRCLE S.p.A.</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -11039,7 +11039,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>ENAV S.p.A.</t>
+          <t>CLASS EDITORI S.p.A.</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -11049,14 +11049,14 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>DATALOGIC S.p.A.</t>
+          <t>CY4Gate S.p.A.</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -11073,7 +11073,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>CY4Gate S.p.A.</t>
+          <t>First Capital S.p.A.</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -11090,7 +11090,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>CLASS EDITORI S.p.A.</t>
+          <t>DATALOGIC S.p.A.</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -11107,7 +11107,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>CIRCLE S.p.A.</t>
+          <t>EQUITA GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -11124,7 +11124,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>CEMBRE S.p.A.</t>
+          <t>Ferretti S.p.A.</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -11134,14 +11134,14 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>CAREL INDUSTRIES S.p.A.</t>
+          <t>FNM S.p.A.</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -11158,7 +11158,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>CAIRO COMMUNICATION S.p.A.</t>
+          <t>FINCANTIERI S.p.A.</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -11168,14 +11168,14 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>BIESSE S.p.A.</t>
+          <t>F.I.L.A. S.p.A.</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -11192,7 +11192,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Aquafil S.p.A.</t>
+          <t>EUROTECH S.p.A.</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -11209,7 +11209,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Altea Green Power S.p.A.</t>
+          <t>ENAV S.p.A.</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -11219,14 +11219,14 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Alfonsino S.p.A.</t>
+          <t>ESAUTOMOTION S.p.A.</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -11243,7 +11243,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Alerion Clean Power S.p.A.</t>
+          <t>Aquafil S.p.A.</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -11260,7 +11260,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>ACEA S.p.A.</t>
+          <t>Alfonsino S.p.A.</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -11270,14 +11270,14 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>ACEA S.p.A.</t>
+          <t>Alerion Clean Power S.p.A.</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -11294,7 +11294,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A2A S.p.A.</t>
+          <t>ACEA S.p.A.</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11304,14 +11304,14 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>GAROFALO HEALTH CARE S.p.A.</t>
+          <t>ACEA S.p.A.</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -11328,7 +11328,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>FNM S.p.A.</t>
+          <t>A2A S.p.A.</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -11345,7 +11345,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>F.I.L.A. S.p.A.</t>
+          <t>Altea Green Power S.p.A.</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11362,7 +11362,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>GVS S.p.A.</t>
+          <t>FIDIA S.p.A</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -11372,14 +11372,14 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>REPLY S.p.A.</t>
+          <t>ERG S.p.A.</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -11396,7 +11396,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Ferretti S.p.A.</t>
+          <t>ERG S.p.A.</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -11406,14 +11406,14 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>doValue S.p.A.</t>
+          <t>EL.EN. S.p.A.</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -11423,14 +11423,14 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>VNE S.p.A.</t>
+          <t>COMPAGNIA DEI CARAIBI S.p.A.</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -11447,7 +11447,7 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>VNE S.p.A.</t>
+          <t>CY4Gate S.p.A.</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -11457,14 +11457,14 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>VINCENZO ZUCCHI S.p.A.</t>
+          <t>CLABO S.p.A.</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -11474,14 +11474,14 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>TAMBURI INVESTMENT PARTNERS S.p.A.</t>
+          <t>AEROPORTO GUGLIELMO MARCONI DI BOLOGNA S.p.A.</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -11491,14 +11491,14 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>FIDIA S.p.A</t>
+          <t>AEROPORTO GUGLIELMO MARCONI DI BOLOGNA S.p.A.</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -11508,14 +11508,14 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>ERG S.p.A.</t>
+          <t>ECOSUNTEK S.p.A.</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -11532,7 +11532,7 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>ERG S.p.A.</t>
+          <t>MARR S.p.A.</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -11542,14 +11542,14 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>EL.EN. S.p.A.</t>
+          <t>Praexidia Industrie Strategiche S.p.A.</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -11559,14 +11559,14 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>ECOSUNTEK S.p.A.</t>
+          <t>doValue S.p.A.</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -11576,14 +11576,14 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>CY4Gate S.p.A.</t>
+          <t>VNE S.p.A.</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -11593,14 +11593,14 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>COMPAGNIA DEI CARAIBI S.p.A.</t>
+          <t>VNE S.p.A.</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -11610,14 +11610,14 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>CLABO S.p.A.</t>
+          <t>VINCENZO ZUCCHI S.p.A.</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -11627,14 +11627,14 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>AEROPORTO GUGLIELMO MARCONI DI BOLOGNA S.p.A.</t>
+          <t>TAMBURI INVESTMENT PARTNERS S.p.A.</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -11644,14 +11644,14 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>AEROPORTO GUGLIELMO MARCONI DI BOLOGNA S.p.A.</t>
+          <t>IRCE s.p.a</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -11668,7 +11668,7 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>MARR S.p.A.</t>
+          <t>INTERPUMP GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -11678,14 +11678,14 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>MARR S.p.A.</t>
+          <t>GVS S.p.A.</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -11695,14 +11695,14 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Praexidia Industrie Strategiche S.p.A.</t>
+          <t>MARR S.p.A.</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -11712,14 +11712,14 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>IRCE s.p.a</t>
+          <t>REPLY S.p.A.</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -11736,7 +11736,7 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>INTERPUMP GROUP S.p.A.</t>
+          <t>SOGES GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -11753,7 +11753,7 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>SOGES GROUP S.p.A.</t>
+          <t>Renovalo S.p.A.</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -11770,7 +11770,7 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Renovalo S.p.A.</t>
+          <t>Ferretti S.p.A.</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -11787,7 +11787,7 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>GREEN OLEO S.p.A</t>
+          <t>SYS-DAT S.p.A.</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -11797,14 +11797,14 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>BESTBE HOLDING S.p.A.</t>
+          <t>OMER S.p.A.</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -11814,14 +11814,14 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>EuroGroup Laminations S.p.A.</t>
+          <t>GREEN OLEO S.p.A</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -11838,7 +11838,7 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>OMER S.p.A.</t>
+          <t>EuroGroup Laminations S.p.A.</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -11855,7 +11855,7 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>SYS-DAT S.p.A.</t>
+          <t>BESTBE HOLDING S.p.A.</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -11865,14 +11865,14 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>Itway S.p.A.</t>
+          <t>Officina Stellare S.p.A.</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -11889,7 +11889,7 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>Officina Stellare S.p.A.</t>
+          <t>Itway S.p.A.</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -11906,7 +11906,7 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>ASSICURAZIONI GENERALI S.p.A.</t>
+          <t>DIADEMA CAPITAL</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -11916,7 +11916,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
@@ -11940,7 +11940,7 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>DIADEMA CAPITAL</t>
+          <t>eVISO S.p.A.</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -11950,14 +11950,14 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>Svas Biosana S.p.A.</t>
+          <t>ASSICURAZIONI GENERALI S.p.A.</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -11967,14 +11967,14 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>eVISO S.p.A.</t>
+          <t>OPS Italia S.p.A.</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -11984,14 +11984,14 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>OPS Italia S.p.A.</t>
+          <t>Svas Biosana S.p.A.</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -12001,14 +12001,14 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>Stellantis N.V.</t>
+          <t>Softlab S.p.A.</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -12018,14 +12018,14 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>ASSICURAZIONI GENERALI S.p.A.</t>
+          <t>Svas Biosana S.p.A.</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -12035,14 +12035,14 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>DOTSTAY S.p.A.</t>
+          <t>Stellantis N.V.</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -12052,14 +12052,14 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>Lemon Sistemi S.p.A.</t>
+          <t>EXPERT.AI S.p.A.</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -12069,14 +12069,14 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>EXPERT.AI S.p.A.</t>
+          <t>IDNTT S.A.</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -12093,7 +12093,7 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>IDNTT S.A.</t>
+          <t>IREN S.p.A.</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -12103,14 +12103,14 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>IREN S.p.A.</t>
+          <t>Industrie De Nora S.p.A.</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -12120,14 +12120,14 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>Met.Extra Group S.p.A.</t>
+          <t>Laboratorio Farmaceutico Erfo S.p.A.</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -12137,14 +12137,14 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>Sanlorenzo S.p.A.</t>
+          <t>Lemon Sistemi S.p.A.</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -12154,14 +12154,14 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>Softlab S.p.A.</t>
+          <t>Sanlorenzo S.p.A.</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -12171,14 +12171,14 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>Industrie De Nora S.p.A.</t>
+          <t>Met.Extra Group S.p.A.</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -12188,14 +12188,14 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>Laboratorio Farmaceutico Erfo S.p.A.</t>
+          <t>ASSICURAZIONI GENERALI S.p.A.</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -12205,14 +12205,14 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>Svas Biosana S.p.A.</t>
+          <t>DOTSTAY S.p.A.</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -12222,14 +12222,14 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>Portobello S.p.A.</t>
+          <t>BRIOSCHI SVILUPPO IMMOBILIARE S.p.A</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -12239,7 +12239,7 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
@@ -12263,7 +12263,7 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>BRIOSCHI SVILUPPO IMMOBILIARE S.p.A</t>
+          <t>Portobello S.p.A.</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -12273,14 +12273,14 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>DHH S.p.A.</t>
+          <t>Sanlorenzo S.p.A.</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -12290,14 +12290,14 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>Farmacosmo S.p.A.</t>
+          <t>Sicily by Car S.p.A.</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -12307,14 +12307,14 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>Sanlorenzo S.p.A.</t>
+          <t>DHH S.p.A.</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -12324,14 +12324,14 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>Sicily by Car S.p.A.</t>
+          <t>Farmacosmo S.p.A.</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -12341,14 +12341,14 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>BRIOSCHI SVILUPPO IMMOBILIARE S.p.A</t>
+          <t>BASTOGI S.p.A.</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -12365,7 +12365,7 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>BASTOGI S.p.A.</t>
+          <t>BRIOSCHI SVILUPPO IMMOBILIARE S.p.A</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -12382,7 +12382,7 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>MEVIM S.p.A.</t>
+          <t>E-NOVIA S.p.A.</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -12399,7 +12399,7 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>Indel B S.p.A.</t>
+          <t>Vivenda Group S.p.A.</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -12409,14 +12409,14 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>E-NOVIA S.p.A.</t>
+          <t>Sicily by Car S.p.A.</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -12426,14 +12426,14 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>DBA GROUP S.p.A.</t>
+          <t>MONDO TV FRANCE</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -12450,7 +12450,7 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>COFLE S.p.A.</t>
+          <t>MEVIM S.p.A.</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -12467,7 +12467,7 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>Sicily by Car S.p.A.</t>
+          <t>Indel B S.p.A.</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -12484,7 +12484,7 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>Vivenda Group S.p.A.</t>
+          <t>DBA GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -12501,7 +12501,7 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>MONDO TV FRANCE</t>
+          <t>COFLE S.p.A.</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -12552,7 +12552,7 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>ATON Green Storage S.p.A.</t>
+          <t>MONDO TV S.p.A.</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -12569,7 +12569,7 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>MONDO TV S.p.A.</t>
+          <t>ATON Green Storage S.p.A.</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -12586,7 +12586,7 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>AEFFE S.p.A.</t>
+          <t>STMicroelectronics N.V.</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -12596,7 +12596,7 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
@@ -12620,7 +12620,7 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>STMicroelectronics N.V.</t>
+          <t>OPS ECOM S.p.A.</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -12630,14 +12630,14 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>OPS ECOM S.p.A.</t>
+          <t>AEFFE S.p.A.</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -12647,14 +12647,14 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>Industrie De Nora S.p.A.</t>
+          <t>AEFFE S.p.A.</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -12664,14 +12664,14 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>AEFFE S.p.A.</t>
+          <t>Industrie De Nora S.p.A.</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -12681,14 +12681,14 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>CROWDFUNDME S.p.A.</t>
+          <t>Piu' Medical S.p.A.</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -12698,14 +12698,14 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>Seri Industrial S.p.A.</t>
+          <t>Renovalo S.p.A.</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -12722,7 +12722,7 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>Ambromobiliare S.p.A.</t>
+          <t>CULTI Milano S.p.A.</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -12739,7 +12739,7 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>Vantea Smart S.p.A.</t>
+          <t>Casta Diva Group S.p.A.</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -12749,14 +12749,14 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>Piu' Medical S.p.A.</t>
+          <t>Cube Labs S.p.A.</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -12773,7 +12773,7 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>CULTI Milano S.p.A.</t>
+          <t>FAE Technology Società Benefit S.p.A.</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -12790,7 +12790,7 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>Casta Diva Group S.p.A.</t>
+          <t>OPS Retail S.p.A.</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -12807,7 +12807,7 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>Cube Labs S.p.A.</t>
+          <t>Vantea Smart S.p.A.</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -12817,14 +12817,14 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>FAE Technology Società Benefit S.p.A.</t>
+          <t>Seri Industrial S.p.A.</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -12841,7 +12841,7 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>Renovalo S.p.A.</t>
+          <t>CROWDFUNDME S.p.A.</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -12858,7 +12858,7 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>OSAI Automation System S.p.A.</t>
+          <t>Ambromobiliare S.p.A.</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -12868,14 +12868,14 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>Otofarma S.p.A.</t>
+          <t>OSAI Automation System S.p.A.</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -12892,7 +12892,7 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>POLIGRAFICI PRINTING S.p.A.</t>
+          <t>Otofarma S.p.A.</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -12902,14 +12902,14 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>OPS Retail S.p.A.</t>
+          <t>POLIGRAFICI PRINTING S.p.A.</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -12919,14 +12919,14 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>Finanza.tech S.p.A. Società Benefit</t>
+          <t>Adventure S.p.A.</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -12936,14 +12936,14 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>EDILIZIACROBATICA S.p.A.</t>
+          <t>CROWDFUNDME S.p.A.</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -12953,14 +12953,14 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>E-Globe S.p.A.</t>
+          <t>EDILIZIACROBATICA S.p.A.</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -12970,14 +12970,14 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>Cloudia Research S.p.A.</t>
+          <t>Finanza.tech S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -12994,7 +12994,7 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>CULTI Milano S.p.A.</t>
+          <t>Gentili Mosconi S.p.A.</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -13004,14 +13004,14 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>CSP INTERNATIONAL FASHION GROUP S.p.A.</t>
+          <t>H-FARM S.p.A.</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -13021,14 +13021,14 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>CROWDFUNDME S.p.A.</t>
+          <t>OVS S.p.A.</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -13045,7 +13045,7 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>Gentili Mosconi S.p.A.</t>
+          <t>TMP Group S.p.A.</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -13055,14 +13055,14 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>ECOSUNTEK S.p.A.</t>
+          <t>Triboo S.p.A.</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -13072,14 +13072,14 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>Adventure S.p.A.</t>
+          <t>POLIGRAFICI PRINTING S.p.A.</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -13089,14 +13089,14 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>OVS S.p.A.</t>
+          <t>ECOSUNTEK S.p.A.</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -13106,14 +13106,14 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>POLIGRAFICI PRINTING S.p.A.</t>
+          <t>E-Globe S.p.A.</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -13130,7 +13130,7 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>TMP Group S.p.A.</t>
+          <t>Cloudia Research S.p.A.</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -13147,7 +13147,7 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>Triboo S.p.A.</t>
+          <t>CULTI Milano S.p.A.</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -13164,7 +13164,7 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>Vantea Smart S.p.A.</t>
+          <t>CSP INTERNATIONAL FASHION GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -13181,7 +13181,7 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>H-FARM S.p.A.</t>
+          <t>Vantea Smart S.p.A.</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -13191,7 +13191,7 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
@@ -13317,7 +13317,7 @@
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>B.F. S.p.A.</t>
+          <t>OLIDATA S.p.A.</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
@@ -13334,7 +13334,7 @@
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>OLIDATA S.p.A.</t>
+          <t>B.F. S.p.A.</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
@@ -13372,78 +13372,9 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Stock</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>CLASS EDITORI S.p.A.</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>2026-05-14</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>COMPAGNIA DEI CARAIBI S.p.A.</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Bod Annual Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>doValue S.p.A.</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>